--- a/originales/respuestas/2025/01. Calificadas/bucle p14/Secretaría Distrital De Salud.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p14/Secretaría Distrital De Salud.xlsx
@@ -438,7 +438,11 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="26" width="10.71"/>
+    <col customWidth="1" min="1" max="2" width="10.71"/>
+    <col customWidth="1" min="3" max="3" width="60.43"/>
+    <col customWidth="1" min="4" max="5" width="10.71"/>
+    <col customWidth="1" min="6" max="6" width="36.29"/>
+    <col customWidth="1" min="7" max="26" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
